--- a/planning/uat/round-0/fixtures-data/good-0012.xlsx
+++ b/planning/uat/round-0/fixtures-data/good-0012.xlsx
@@ -35,7 +35,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">UAT IMP-01 184405 item 1</t>
+          <t xml:space="preserve">UAT IMP-01 190749 item 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
